--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484853_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484853_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.098</v>
+        <v>5.0863</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5687</v>
+        <v>1.848</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5293</v>
+        <v>3.2383</v>
       </c>
       <c r="G2" t="n">
         <v>0.7562</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>2.021</v>
+        <v>1.0094</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0175</v>
+        <v>0.2968</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0035</v>
+        <v>0.7125</v>
       </c>
       <c r="V2" t="n">
         <v>2.1886</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>E. ZOROA GARCIA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1487</v>
+        <v>5.0062</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9483</v>
+        <v>3.0435</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2003</v>
+        <v>1.9627</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3562</v>
+        <v>2.299</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.0103</v>
+        <v>0.9352</v>
       </c>
       <c r="I3" t="n">
-        <v>5.3665</v>
+        <v>1.3638</v>
       </c>
       <c r="J3" t="n">
-        <v>5.3862</v>
+        <v>1.4656</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.5862000000000001</v>
+        <v>0.7082000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9724</v>
+        <v>0.7574</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.03</v>
+        <v>0.8334</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4241</v>
+        <v>0.227</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6059</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.7548</v>
+        <v>0.7548</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1322</v>
+        <v>0.7548</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9247</v>
+        <v>0.4053</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2039</v>
+        <v>0.0308</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7208</v>
+        <v>0.3745</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6226</v>
+        <v>1.547</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2452</v>
+        <v>1.547</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. ZOROA GARCIA</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.5409</v>
+        <v>4.9776</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7898</v>
+        <v>4.8716</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7511</v>
+        <v>0.1061</v>
       </c>
       <c r="G4" t="n">
-        <v>2.299</v>
+        <v>1.7691</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9352</v>
+        <v>-0.0837</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3638</v>
+        <v>1.8528</v>
       </c>
       <c r="J4" t="n">
-        <v>1.4656</v>
+        <v>3.26</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7082000000000001</v>
+        <v>1.1042</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7574</v>
+        <v>2.1558</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8334</v>
+        <v>-1.4909</v>
       </c>
       <c r="N4" t="n">
-        <v>0.227</v>
+        <v>-1.188</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6064000000000001</v>
+        <v>-0.303</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.7548</v>
+        <v>1.1322</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0599</v>
+        <v>1.1329</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2228</v>
+        <v>0.3663</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1629</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>1.547</v>
+        <v>0.9434</v>
       </c>
       <c r="W4" t="n">
-        <v>1.547</v>
+        <v>1.2452</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.4414</v>
+        <v>4.9719</v>
       </c>
       <c r="E5" t="n">
-        <v>4.5205</v>
+        <v>4.8509</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0791</v>
+        <v>0.121</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7691</v>
+        <v>4.3562</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0837</v>
+        <v>-1.0103</v>
       </c>
       <c r="I5" t="n">
-        <v>1.8528</v>
+        <v>5.3665</v>
       </c>
       <c r="J5" t="n">
-        <v>3.26</v>
+        <v>5.3862</v>
       </c>
       <c r="K5" t="n">
-        <v>1.1042</v>
+        <v>-0.5862000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1558</v>
+        <v>5.9724</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.4909</v>
+        <v>-1.03</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.188</v>
+        <v>-0.4241</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.303</v>
+        <v>-0.6059</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1322</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R5" t="n">
         <v>1.1322</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5967</v>
+        <v>0.7479</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0152</v>
+        <v>0.1065</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5814</v>
+        <v>0.6414</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9434</v>
+        <v>0.6226</v>
       </c>
       <c r="W5" t="n">
         <v>1.2452</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.3018</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.597</v>
+        <v>3.5378</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3322</v>
+        <v>1.3523</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2648</v>
+        <v>2.1854</v>
       </c>
       <c r="G6" t="n">
         <v>2.1231</v>
@@ -922,13 +922,13 @@
         <v>0.9435</v>
       </c>
       <c r="S6" t="n">
-        <v>1.1722</v>
+        <v>1.113</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1916</v>
+        <v>0.2117</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9806</v>
+        <v>0.9012</v>
       </c>
       <c r="V6" t="n">
         <v>1.2452</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1512</v>
+        <v>2.5132</v>
       </c>
       <c r="E7" t="n">
-        <v>2.014</v>
+        <v>2.1115</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1372</v>
+        <v>0.4018</v>
       </c>
       <c r="G7" t="n">
         <v>2.5813</v>
@@ -1000,13 +1000,13 @@
         <v>1.5096</v>
       </c>
       <c r="S7" t="n">
-        <v>0.532</v>
+        <v>0.894</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1328</v>
+        <v>0.2302</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3992</v>
+        <v>0.6637</v>
       </c>
       <c r="V7" t="n">
         <v>-0.5846</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DIEZ RUANO</t>
+          <t>J. ESTRELLA MATOS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4737</v>
+        <v>1.1988</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1341</v>
+        <v>0.4388</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6078</v>
+        <v>0.76</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5619</v>
+        <v>1.775</v>
       </c>
       <c r="H8" t="n">
-        <v>0.432</v>
+        <v>-0.3592</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1299</v>
+        <v>2.1342</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0423</v>
+        <v>2.3879</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0423</v>
+        <v>0.4703</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.9175</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5196</v>
+        <v>-0.6128</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3897</v>
+        <v>-0.8295</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1299</v>
+        <v>0.2167</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0882</v>
+        <v>0.8198</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1764</v>
+        <v>-0.0621</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0882</v>
+        <v>0.8818</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.2072</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2072</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. ESTRELLA MATOS</t>
+          <t>A. DIEZ RUANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4496</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2046</v>
+        <v>-0.07530000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6542</v>
+        <v>0.7401</v>
       </c>
       <c r="G9" t="n">
-        <v>1.775</v>
+        <v>0.5619</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3592</v>
+        <v>0.432</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1342</v>
+        <v>0.1299</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3879</v>
+        <v>0.0423</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4703</v>
+        <v>0.0423</v>
       </c>
       <c r="L9" t="n">
-        <v>1.9175</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6128</v>
+        <v>0.5196</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8295</v>
+        <v>0.3897</v>
       </c>
       <c r="O9" t="n">
-        <v>0.2167</v>
+        <v>0.1299</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6983</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1029</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7055</v>
+        <v>-0.1176</v>
       </c>
       <c r="U9" t="n">
-        <v>0.776</v>
+        <v>0.2205</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2072</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2072</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1116</v>
+        <v>0.0789</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2814</v>
+        <v>-2.2613</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3931</v>
+        <v>2.3402</v>
       </c>
       <c r="G10" t="n">
         <v>0.4945</v>
@@ -1234,13 +1234,13 @@
         <v>1.3209</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8248</v>
+        <v>0.792</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1023</v>
+        <v>-0.0822</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9271</v>
+        <v>0.8742</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6415999999999999</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.0101</v>
+        <v>-1.283</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2821</v>
+        <v>-1.1846</v>
       </c>
       <c r="F11" t="n">
-        <v>0.272</v>
+        <v>-0.0984</v>
       </c>
       <c r="G11" t="n">
         <v>0.2772</v>
@@ -1312,13 +1312,13 @@
         <v>1.3209</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4485</v>
+        <v>1.1756</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1916</v>
+        <v>0.289</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2569</v>
+        <v>0.8865</v>
       </c>
       <c r="V11" t="n">
         <v>-1.2262</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4192</v>
+        <v>-1.5817</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.9395</v>
+        <v>-1.0756</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.4797</v>
+        <v>-0.5062</v>
       </c>
       <c r="G12" t="n">
         <v>0.402</v>
@@ -1390,13 +1390,13 @@
         <v>1.3209</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5754</v>
+        <v>1.4129</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4884</v>
+        <v>0.3524</v>
       </c>
       <c r="U12" t="n">
-        <v>1.087</v>
+        <v>1.0605</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>24.5828</v>
+        <v>25.1708</v>
       </c>
       <c r="E13" t="n">
-        <v>13.3318</v>
+        <v>13.9198</v>
       </c>
       <c r="F13" t="n">
         <v>11.251</v>
@@ -1444,7 +1444,7 @@
         <v>21.8475</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7433</v>
+        <v>0.7432999999999997</v>
       </c>
       <c r="L13" t="n">
         <v>21.1042</v>
@@ -1468,13 +1468,13 @@
         <v>12.2655</v>
       </c>
       <c r="S13" t="n">
-        <v>9.0177</v>
+        <v>9.605700000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>1.034</v>
+        <v>1.6218</v>
       </c>
       <c r="U13" t="n">
-        <v>7.9836</v>
+        <v>7.9834</v>
       </c>
       <c r="V13" t="n">
         <v>2.8872</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.4698</v>
+        <v>2.3231</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3149</v>
+        <v>3.12</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.845</v>
+        <v>-0.7968</v>
       </c>
       <c r="G14" t="n">
         <v>2.8809</v>
@@ -1546,13 +1546,13 @@
         <v>2.0757</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.5432</v>
+        <v>-0.6898</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3375</v>
+        <v>-0.5324</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2057</v>
+        <v>-0.1575</v>
       </c>
       <c r="V14" t="n">
         <v>0.3208</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>L. FUENTES GOMEZ</t>
+          <t>P. TORMO HERRERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8399</v>
+        <v>-1.3375</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0186</v>
+        <v>-0.2741</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.8585</v>
+        <v>-1.0635</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.6261</v>
+        <v>-1.726</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2622</v>
+        <v>2.8831</v>
       </c>
       <c r="I16" t="n">
-        <v>-2.364</v>
+        <v>-4.6091</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5039</v>
+        <v>1.8635</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0634</v>
+        <v>3.0959</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5673</v>
+        <v>-1.2324</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1222</v>
+        <v>-3.5895</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3256</v>
+        <v>-0.2128</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7967</v>
+        <v>-3.3767</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3774</v>
+        <v>2.0757</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.1887</v>
+        <v>-0.3774</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5661</v>
+        <v>2.4531</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7107</v>
+        <v>-1.0457</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7112000000000001</v>
+        <v>-1.1186</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0.07290000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3018</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MAS MICO</t>
+          <t>D. HOLGADO CUELLAR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9718</v>
+        <v>-1.6057</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3369</v>
+        <v>-0.0859</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6349</v>
+        <v>-1.5199</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.5267</v>
+        <v>0.2442</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1878</v>
+        <v>0.4649</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.7146</v>
+        <v>-0.2207</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4428</v>
+        <v>2.741</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0423</v>
+        <v>0.8405</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.485</v>
+        <v>1.9005</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.084</v>
+        <v>-2.4968</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1456</v>
+        <v>-0.3756</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.2295</v>
+        <v>-2.1212</v>
       </c>
       <c r="P17" t="n">
-        <v>1.3209</v>
+        <v>0.5661</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5096</v>
+        <v>2.4531</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.766</v>
+        <v>-1.4347</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7055</v>
+        <v>-1.2037</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0605</v>
+        <v>-0.231</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.9813</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2639</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. TORMO HERRERO</t>
+          <t>J. MAS MICO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.1542</v>
+        <v>-1.6916</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5664</v>
+        <v>-1.2395</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5878</v>
+        <v>-0.4521</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.726</v>
+        <v>-2.5267</v>
       </c>
       <c r="H18" t="n">
-        <v>2.8831</v>
+        <v>0.1878</v>
       </c>
       <c r="I18" t="n">
-        <v>-4.6091</v>
+        <v>-2.7146</v>
       </c>
       <c r="J18" t="n">
-        <v>1.8635</v>
+        <v>-0.4428</v>
       </c>
       <c r="K18" t="n">
-        <v>3.0959</v>
+        <v>0.0423</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2324</v>
+        <v>-0.485</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.5895</v>
+        <v>-2.084</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2128</v>
+        <v>0.1456</v>
       </c>
       <c r="O18" t="n">
-        <v>-3.3767</v>
+        <v>-2.2295</v>
       </c>
       <c r="P18" t="n">
-        <v>2.0757</v>
+        <v>1.3209</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.3774</v>
+        <v>-0.1887</v>
       </c>
       <c r="R18" t="n">
-        <v>2.4531</v>
+        <v>1.5096</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8623</v>
+        <v>-0.4857</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.4109</v>
+        <v>-0.608</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4514</v>
+        <v>0.1223</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6415999999999999</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. HOLGADO CUELLAR</t>
+          <t>L. FUENTES GOMEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1686</v>
+        <v>-2.3836</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2807</v>
+        <v>-0.7608</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.8879</v>
+        <v>-1.6228</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2442</v>
+        <v>-2.6261</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4649</v>
+        <v>-0.2622</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2207</v>
+        <v>-2.364</v>
       </c>
       <c r="J19" t="n">
-        <v>2.741</v>
+        <v>-0.5039</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8405</v>
+        <v>0.0634</v>
       </c>
       <c r="L19" t="n">
-        <v>1.9005</v>
+        <v>-0.5673</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4968</v>
+        <v>-2.1222</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3756</v>
+        <v>-0.3256</v>
       </c>
       <c r="O19" t="n">
-        <v>-2.1212</v>
+        <v>-1.7967</v>
       </c>
       <c r="P19" t="n">
+        <v>0.3774</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-0.1887</v>
+      </c>
+      <c r="R19" t="n">
         <v>0.5661</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-1.887</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.4531</v>
-      </c>
       <c r="S19" t="n">
-        <v>-1.9975</v>
+        <v>0.1669</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3986</v>
+        <v>-0.0682</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.599</v>
+        <v>0.2352</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9813</v>
+        <v>-0.3018</v>
       </c>
       <c r="W19" t="n">
-        <v>0.2639</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2452</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.1724</v>
+        <v>-2.8657</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1551</v>
+        <v>-1.0577</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.0173</v>
+        <v>-1.808</v>
       </c>
       <c r="G20" t="n">
         <v>-2.0467</v>
@@ -2014,13 +2014,13 @@
         <v>0.7548</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7483</v>
+        <v>-0.4416</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7642</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0159</v>
+        <v>0.2252</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2237</v>
+        <v>-3.3222</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.5589</v>
+        <v>-3.3641</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3352</v>
+        <v>0.0418</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1582</v>
@@ -2092,13 +2092,13 @@
         <v>3.3966</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4049</v>
+        <v>-1.5034</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.8689</v>
+        <v>-1.674</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4639</v>
+        <v>0.1706</v>
       </c>
       <c r="V21" t="n">
         <v>1.2072</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5208</v>
+        <v>-5.4944</v>
       </c>
       <c r="E22" t="n">
         <v>-3.3045</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2163</v>
+        <v>-2.1899</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6762</v>
@@ -2170,13 +2170,13 @@
         <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7125</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="T22" t="n">
         <v>-0.823</v>
       </c>
       <c r="U22" t="n">
-        <v>0.1105</v>
+        <v>0.137</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2452</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.7363</v>
+        <v>-6.6412</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.8413</v>
+        <v>-3.7439</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.895</v>
+        <v>-2.8973</v>
       </c>
       <c r="G23" t="n">
         <v>-5.3239</v>
@@ -2248,13 +2248,13 @@
         <v>2.4531</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1863</v>
+        <v>-1.0912</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.1046</v>
+        <v>-1.0072</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.08160000000000001</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V23" t="n">
         <v>-1.547</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-24.5827</v>
+        <v>-23.2836</v>
       </c>
       <c r="E24" t="n">
-        <v>-11.2508</v>
+        <v>-11.251</v>
       </c>
       <c r="F24" t="n">
-        <v>-13.3318</v>
+        <v>-12.0328</v>
       </c>
       <c r="G24" t="n">
         <v>-17.3954</v>
@@ -2299,13 +2299,13 @@
         <v>-21.2147</v>
       </c>
       <c r="J24" t="n">
-        <v>4.4519</v>
+        <v>4.451900000000002</v>
       </c>
       <c r="K24" t="n">
         <v>4.562399999999998</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.1103</v>
+        <v>-0.1102999999999996</v>
       </c>
       <c r="M24" t="n">
         <v>-21.8474</v>
@@ -2326,13 +2326,13 @@
         <v>16.983</v>
       </c>
       <c r="S24" t="n">
-        <v>-9.0176</v>
+        <v>-7.7185</v>
       </c>
       <c r="T24" t="n">
-        <v>-7.983599999999999</v>
+        <v>-7.9835</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0342</v>
+        <v>0.2650000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>-2.8871</v>
